--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Scrum/07_Sprint_Backlog_CitaJusta.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Scrum/07_Sprint_Backlog_CitaJusta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EB5887-C46D-4A5D-B0AE-B4804FEAB5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40C3F1C-D36C-4E57-91B9-9405CF8A8815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="110">
   <si>
     <t>Campo</t>
   </si>
@@ -142,334 +142,175 @@
     <t>Restante final</t>
   </si>
   <si>
+    <t>S6-T01</t>
+  </si>
+  <si>
+    <t>Tarea completada técnicamente; horas diarias no reconstruidas retrospectivamente.</t>
+  </si>
+  <si>
+    <t>S6-T02</t>
+  </si>
+  <si>
+    <t>S6-T03</t>
+  </si>
+  <si>
+    <t>S6-T04</t>
+  </si>
+  <si>
+    <t>S6-T05</t>
+  </si>
+  <si>
+    <t>S6-T06</t>
+  </si>
+  <si>
+    <t>S6-T07</t>
+  </si>
+  <si>
+    <t>Tarea completada y validada; horas diarias no reconstruidas retrospectivamente.</t>
+  </si>
+  <si>
+    <t>S6-T08</t>
+  </si>
+  <si>
+    <t>Validación integrada completada con escenarios reales de expiración, aceptación y rechazo.</t>
+  </si>
+  <si>
+    <t>S6-T09</t>
+  </si>
+  <si>
+    <t>HU-023 completada y mergeada. Horas diarias no reconstruidas retrospectivamente.</t>
+  </si>
+  <si>
+    <t>S6-T10</t>
+  </si>
+  <si>
+    <t>HU-024 completada y mergeada. Prueba manual de centro de notificaciones y persistencia de lectura PASS.</t>
+  </si>
+  <si>
+    <t>Entregables logrados</t>
+  </si>
+  <si>
+    <t>Pendientes del Sprint</t>
+  </si>
+  <si>
+    <t>CITAJUSTA SPRINT BACKLOG — SPRINT 7 EN PROGRESO</t>
+  </si>
+  <si>
+    <t>Versión 1.6 · 23-09-2026 · Sprint 7 activo · HU-027, HU-028 y HU-029 completadas y mergeadas a main · siguiente PBI Desktop pendiente de refinamiento.</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>En progreso</t>
+  </si>
+  <si>
+    <t>23-09-2026</t>
+  </si>
+  <si>
+    <t>Sprint 7 está en progreso. HU-027, HU-028 y HU-029 están Done. HU-019/HU-020 backend ya estaban implementadas como prerrequisitos institucionales. El siguiente PBI Desktop no se agrega hasta su refinamiento; no se reconstruyen horas ni se altera el Burndown histórico de Sprint 6.</t>
+  </si>
+  <si>
+    <t>HU-027</t>
+  </si>
+  <si>
+    <t>S7-T01</t>
+  </si>
+  <si>
+    <t>Inicializar aplicación Desktop institucional con Tauri</t>
+  </si>
+  <si>
+    <t>Desktop / Fundación</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Monorepo + API existente</t>
+  </si>
+  <si>
+    <t>apps/desktop compila y abre como cliente nativo; shell institucional preparada sin lógica de negocio duplicada</t>
+  </si>
+  <si>
+    <t>feat/desktop-tauri-foundation · PR #112 · merge 6adab82</t>
+  </si>
+  <si>
+    <t>Commit 01ff1b1. Build frontend y cargo check PASS; ejecución nativa validada.</t>
+  </si>
+  <si>
+    <t>HU-028</t>
+  </si>
+  <si>
+    <t>S7-T02</t>
+  </si>
+  <si>
+    <t>Implementar autenticación Desktop y cliente compartido</t>
+  </si>
+  <si>
+    <t>Desktop / Integración</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>HU-027 + Auth API</t>
+  </si>
+  <si>
+    <t>Login/logout reales, contexto institucional y cliente compartido sin persistencia insegura de tokens</t>
+  </si>
+  <si>
+    <t>feat/desktop-auth-api · PR #113 · merge ae151b3</t>
+  </si>
+  <si>
+    <t>Web 95/95; Desktop 7/7; client-core 2/2; build/cargo PASS; login/logout manual PASS.</t>
+  </si>
+  <si>
+    <t>HU-029</t>
+  </si>
+  <si>
+    <t>S7-T03</t>
+  </si>
+  <si>
+    <t>Gestionar sedes y servicios desde Desktop</t>
+  </si>
+  <si>
+    <t>Desktop / Backend / Integración</t>
+  </si>
+  <si>
+    <t>HU-012 + HU-028 + RBAC</t>
+  </si>
+  <si>
+    <t>Lecturas administrativas y CRUD institucional respetan tenant/scope; categorías y branchIds reales; GET públicos sin regresión</t>
+  </si>
+  <si>
+    <t>feat/desktop-branch-service-management · commit f58c742 · merge e1cdb2e</t>
+  </si>
+  <si>
+    <t>API 394/394; backend 34/34; E2E 15/15; Web 95/95; Desktop 16/16; client-core 4/4; prueba manual CRUD Tauri PASS.</t>
+  </si>
+  <si>
+    <t>SIGUIENTE PBI DE SPRINT 7: pendiente de refinamiento. No se documenta HU-030 hasta definir alcance y criterios con evidencia real.</t>
+  </si>
+  <si>
+    <t>CONTROL DIARIO SPRINT 6 — EVIDENCIA HISTÓRICA CONSERVADA</t>
+  </si>
+  <si>
+    <t>Sprint 6 permanece cerrado y no se reconstruyen horas históricas. Sprint 7 está en progreso con HU-027 a HU-029 Done; sus horas no se inventan ni se incorporan retroactivamente a este control.</t>
+  </si>
+  <si>
+    <t>CITAJUSTA — RESUMEN SPRINT 7 EN PROGRESO</t>
+  </si>
+  <si>
     <t>Indicador</t>
   </si>
   <si>
     <t>Tareas</t>
   </si>
   <si>
-    <t>Entregables logrados</t>
-  </si>
-  <si>
-    <t>Pendientes del Sprint</t>
-  </si>
-  <si>
-    <t>CITAJUSTA SPRINT BACKLOG — SPRINT 6 CERRADO + TRANSICIÓN A SPRINT 7</t>
-  </si>
-  <si>
-    <t>Versión 1.5 · 22-09-2026 · Sprint 6 cerrado con 10/10 tareas · HU-025 y HU-026 completadas como cierre Web posterior antes de Desktop/Tauri.</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Cerrado</t>
-  </si>
-  <si>
-    <t>22-09-2026</t>
-  </si>
-  <si>
-    <t>Sprint 6 permanece cerrado con 10/10 tareas Done. HU-025 y HU-026 se completaron después del cierre como checkpoint de transición hacia Sprint 7: inicio automático de reasignación al cancelar y búsqueda Web por fecha específica/flexible. No se reconstruyen dentro del Burndown de Sprint 6.</t>
-  </si>
-  <si>
-    <t>HU-009</t>
-  </si>
-  <si>
-    <t>S6-T01</t>
-  </si>
-  <si>
-    <t>Generar oferta de cupo liberado</t>
-  </si>
-  <si>
-    <t>Backend</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>HU-006 + HU-007/008</t>
-  </si>
-  <si>
-    <t>Oferta compatible creada con ranking/snapshot, TTL y trazabilidad</t>
-  </si>
-  <si>
-    <t>feat/reassignment-offers</t>
-  </si>
-  <si>
-    <t>Backend implementado y validado.</t>
-  </si>
-  <si>
-    <t>HU-010</t>
-  </si>
-  <si>
-    <t>S6-T02</t>
-  </si>
-  <si>
-    <t>Aceptar una oferta vigente</t>
-  </si>
-  <si>
-    <t>Aceptación transaccional transfiere la cita y reserva el cupo sin duplicados</t>
-  </si>
-  <si>
-    <t>feat/accept-reassignment-offer</t>
-  </si>
-  <si>
-    <t>Aceptación idempotente y concurrente validada.</t>
-  </si>
-  <si>
-    <t>HU-011</t>
-  </si>
-  <si>
-    <t>S6-T03</t>
-  </si>
-  <si>
-    <t>Rechazar una oferta y continuar flujo</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Rechazo deja waitlist activa y permite siguiente oferta o agotamiento</t>
-  </si>
-  <si>
-    <t>feat/reject-reassignment-offer</t>
-  </si>
-  <si>
-    <t>Rechazo/continuidad implementados.</t>
-  </si>
-  <si>
-    <t>HU-016</t>
-  </si>
-  <si>
-    <t>S6-T04</t>
-  </si>
-  <si>
-    <t>Supervisar una reasignación</t>
-  </si>
-  <si>
-    <t>HU-009/010/011</t>
-  </si>
-  <si>
-    <t>Consulta read-only expone trazabilidad controlada del proceso</t>
-  </si>
-  <si>
-    <t>feat/reassignment-supervision</t>
-  </si>
-  <si>
-    <t>Supervisión backend completada.</t>
-  </si>
-  <si>
-    <t>HU-018</t>
-  </si>
-  <si>
-    <t>S6-T05</t>
-  </si>
-  <si>
-    <t>Configurar reglas de reasignación</t>
-  </si>
-  <si>
-    <t>Políticas versionadas e inmutables configurables por institución</t>
-  </si>
-  <si>
-    <t>feat/reassignment-policy</t>
-  </si>
-  <si>
-    <t>Políticas PRIORITY_THEN_WAITING / WAITING_THEN_PRIORITY implementadas.</t>
-  </si>
-  <si>
-    <t>HU-021</t>
-  </si>
-  <si>
-    <t>S6-T06</t>
-  </si>
-  <si>
-    <t>Gestionar lista de espera y preferencias desde la Web</t>
-  </si>
-  <si>
-    <t>Frontend / Integración</t>
-  </si>
-  <si>
-    <t>HU-007/008 + apps/web</t>
-  </si>
-  <si>
-    <t>Alta, preferencias, persistencia y retiro funcionan contra API/PostgreSQL real</t>
-  </si>
-  <si>
-    <t>feat/web-waitlist · PR #89 · merge c291d17</t>
-  </si>
-  <si>
-    <t>Web 56/56; development/seed 11/11; Waitlist E2E 24/24. Flujo manual completo PASS.</t>
-  </si>
-  <si>
-    <t>HU-022</t>
-  </si>
-  <si>
-    <t>S6-T07</t>
-  </si>
-  <si>
-    <t>Gestionar ofertas de reasignación desde la Web</t>
-  </si>
-  <si>
-    <t>HU-009/010/011 + apps/web</t>
-  </si>
-  <si>
-    <t>Usuario puede ver oferta real, expiresAt, aceptar/rechazar y observar estado final sin lógica crítica en cliente</t>
-  </si>
-  <si>
-    <t>feat/web-reassignment-offers · PR #93 · merge 5701ab7</t>
-  </si>
-  <si>
-    <t>Web /ofertas validada con ACCEPT/REJECT/expiración visual. Mergeada a main mediante PR #93.</t>
-  </si>
-  <si>
-    <t>Técnica</t>
-  </si>
-  <si>
-    <t>S6-T08</t>
-  </si>
-  <si>
-    <t>Validar flujo Web/API/PostgreSQL de ofertas y reasignación</t>
-  </si>
-  <si>
-    <t>Testing / Integración</t>
-  </si>
-  <si>
-    <t>Flujo integrado validado con contratos reales, concurrencia y errores controlados</t>
-  </si>
-  <si>
-    <t>feat/web-reassignment-offers · PR #93</t>
-  </si>
-  <si>
-    <t>Validación Web + API + PostgreSQL completada; ACCEPT transfiere cita existente y REJECT no crea cita.</t>
-  </si>
-  <si>
-    <t>HU-023</t>
-  </si>
-  <si>
-    <t>S6-T09</t>
-  </si>
-  <si>
-    <t>Automatizar expiración de ofertas y continuidad de reasignación</t>
-  </si>
-  <si>
-    <t>Backend / Runner</t>
-  </si>
-  <si>
-    <t>HU-009/010/011 + HU-018</t>
-  </si>
-  <si>
-    <t>Oferta vencida pasa a EXPIRED; continuidad idempotente genera siguiente oferta o cierra EXHAUSTED/CANCELLED de forma segura</t>
-  </si>
-  <si>
-    <t>feat/automatic-offer-expiration · PR #96 · merge 109b1c9</t>
-  </si>
-  <si>
-    <t>API 368/368; E2E expiry 10/10; reasignaciones 20/20; audit 11/11; policy 13/13; reports 15/15; checkpoint 1/1.</t>
-  </si>
-  <si>
-    <t>HU-024</t>
-  </si>
-  <si>
-    <t>S6-T10</t>
-  </si>
-  <si>
-    <t>Implementar notificaciones internas</t>
-  </si>
-  <si>
-    <t>Backend / Web</t>
-  </si>
-  <si>
-    <t>HU-004/006/007/008/009/010/011/023</t>
-  </si>
-  <si>
-    <t>Ocho eventos generan notificaciones deduplicadas; usuario consulta sólo las propias, marca lectura y Web muestra contador/listado persistente</t>
-  </si>
-  <si>
-    <t>feat/internal-notifications · PR #99 · merge b1bff30</t>
-  </si>
-  <si>
-    <t>API nuevos 6/6; E2E notifications 8/8; API dirigida 157/157; regresión crítica 87/87; Web 83/83; prueba manual lectura + logout/login PASS.</t>
-  </si>
-  <si>
-    <t>HITOS POSTERIORES AL CIERRE DE SPRINT 6 — TRANSICIÓN A SPRINT 7</t>
-  </si>
-  <si>
-    <t>HU-025</t>
-  </si>
-  <si>
-    <t>TRANS-01</t>
-  </si>
-  <si>
-    <t>Iniciar automáticamente la reasignación tras una cancelación</t>
-  </si>
-  <si>
-    <t>Backend / Integración</t>
-  </si>
-  <si>
-    <t>HU-006 + motor de reasignación</t>
-  </si>
-  <si>
-    <t>Cancelación reutilizable inicia proceso/oferta automáticamente sin duplicados</t>
-  </si>
-  <si>
-    <t>feat/automatic-reassignment-start · PR #105 · merge ea33e9f</t>
-  </si>
-  <si>
-    <t>API 390/390; E2E 8/8; build/regresión PASS.</t>
-  </si>
-  <si>
-    <t>HU-026</t>
-  </si>
-  <si>
-    <t>TRANS-02</t>
-  </si>
-  <si>
-    <t>Mejorar búsqueda de disponibilidad por fecha</t>
-  </si>
-  <si>
-    <t>HU-003 + apps/web</t>
-  </si>
-  <si>
-    <t>Fecha específica y modo flexible 7/14/30 consultan disponibilidad real con fechas locales válidas</t>
-  </si>
-  <si>
-    <t>feat/availability-date-search · PR #107 · merge ec427a4</t>
-  </si>
-  <si>
-    <t>Fechas 10/10; UI 16/16; Web 95/95; typecheck/build PASS; prueba manual 4 cupos.</t>
-  </si>
-  <si>
-    <t>Siguiente foco: crear/refinar HU-027 e iniciar la fundación Desktop/Tauri institucional desde main limpio.</t>
-  </si>
-  <si>
-    <t>CONTROL DIARIO SPRINT 6 — REGISTRO REAL DE HORAS / TRABAJO RESTANTE</t>
-  </si>
-  <si>
-    <t>No se reconstruyen horas históricas. S6-T01 a S6-T10 pertenecen al Sprint 6 cerrado. HU-025 y HU-026 se completaron posteriormente como transición a Sprint 7 y no se incorporan retroactivamente al control horario ni al Burndown de Sprint 6.</t>
-  </si>
-  <si>
-    <t>Tarea completada técnicamente; horas diarias no reconstruidas retrospectivamente.</t>
-  </si>
-  <si>
-    <t>Tarea completada y validada; horas diarias no reconstruidas retrospectivamente.</t>
-  </si>
-  <si>
-    <t>Validación integrada completada con escenarios reales de expiración, aceptación y rechazo.</t>
-  </si>
-  <si>
-    <t>HU-023 completada y mergeada. Horas diarias no reconstruidas retrospectivamente.</t>
-  </si>
-  <si>
-    <t>HU-024 completada y mergeada. Prueba manual de centro de notificaciones y persistencia de lectura PASS.</t>
-  </si>
-  <si>
-    <t>CITAJUSTA — RESUMEN SPRINT 6 CERRADO + CHECKPOINT WEB POSTERIOR</t>
-  </si>
-  <si>
-    <t>Tareas planificadas</t>
+    <t>Historias refinadas actuales</t>
   </si>
   <si>
     <t>Estimación horaria</t>
@@ -481,57 +322,54 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Tareas Done</t>
+    <t>Historias Done</t>
   </si>
   <si>
     <t>Pendiente</t>
   </si>
   <si>
-    <t>Tareas Ready</t>
+    <t>Historias Ready</t>
   </si>
   <si>
     <t>Ready</t>
   </si>
   <si>
-    <t>Tareas pendientes</t>
+    <t>Pendientes dentro de lo refinado</t>
   </si>
   <si>
     <t>Bloqueado</t>
   </si>
   <si>
-    <t>Avance por tareas</t>
+    <t>Avance de historias refinadas</t>
   </si>
   <si>
     <t>Validación actual</t>
   </si>
   <si>
-    <t>Sprint 6: HU-023 API 368/368 + expiry 10/10 · HU-024 Web 83/83 + notifications 8/8 · Post-S6: HU-025 API 390/390/E2E 8/8 · HU-026 Web 95/95</t>
+    <t>HU-027 Tauri/build/cargo PASS · HU-028 Web 95/95 + Desktop 7/7 + client-core 2/2 · HU-029 API 394/394 + E2E 15/15 + Desktop 16/16</t>
   </si>
   <si>
     <t>Pruebas actuales</t>
   </si>
   <si>
-    <t>HU-023/HU-024 PASS dentro de Sprint 6. HU-025/HU-026 PASS como cierre Web posterior, sin alterar el Burndown histórico del Sprint 6.</t>
-  </si>
-  <si>
-    <t>• HU-009/010/011/016/018 backend completadas.
-• HU-021 Web waitlist/preferencias Done (PR #89).
-• HU-022 Web ofertas Done (PR #93).
-• HU-023 expiración automática/continuidad Done (PR #96).
-• HU-024 notificaciones internas + centro Web Done (PR #99).
-• RF-029/RF-030/RF-034 cerrados con evidencia automática y manual.</t>
-  </si>
-  <si>
-    <t>• Ningún pendiente técnico dentro del Sprint 6 cerrado.
-• HU-025 y HU-026 ya están Done y mergeadas.
-• Actualizar evidencias Scrum con PR #105/#107.
-• Siguiente bloque: fundación Desktop/Tauri institucional.</t>
-  </si>
-  <si>
-    <t>Evidencia técnica al 22-09-2026</t>
-  </si>
-  <si>
-    <t>Sprint 6 permanece cerrado con 10/10 tareas Done. HU-025 (PR #105) y HU-026 (PR #107) completaron posteriormente el cierre funcional del MVP Web y preparan el inicio de Sprint 7 / Desktop/Tauri.</t>
+    <t>HU-027 a HU-029 PASS. Sprint 7 no se marca cerrado: el siguiente PBI Desktop permanece pendiente de refinamiento.</t>
+  </si>
+  <si>
+    <t>• HU-027: fundación Tauri 2 + shell institucional Done (PR #112).
+• HU-028: autenticación Desktop + @citajusta/client-core Done (PR #113).
+• HU-029: gestión real de sedes/servicios Done (merge e1cdb2e).
+• Validación manual Tauri/PostgreSQL de HU-029 completada.</t>
+  </si>
+  <si>
+    <t>• Refinar el siguiente PBI de Sprint 7 antes de incorporarlo.
+• Continuar progresivamente con módulos institucionales soportados por backend.
+• Mantener evidencias Scrum/GitHub sincronizadas.</t>
+  </si>
+  <si>
+    <t>Evidencia técnica al 23-09-2026</t>
+  </si>
+  <si>
+    <t>Sprint 7 está en progreso. HU-027, HU-028 y HU-029 están Done e integradas a main. El Desktop ya posee fundación Tauri, autenticación real y primer módulo institucional funcional (Sedes y servicios).</t>
   </si>
 </sst>
 </file>
@@ -602,7 +440,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -636,14 +474,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -832,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -891,6 +723,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -914,7 +756,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -954,6 +795,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -973,26 +815,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1104,7 +932,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="156082"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:noFill/>
@@ -1118,7 +946,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1159,7 +987,7 @@
               </c15:filteredCategoryTitle>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B42E-4317-A336-14F6914AFC83}"/>
+              <c16:uniqueId val="{00000000-C6E6-4E2A-868A-00572E014641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1351,7 +1179,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_1" displayName="Tabla_1" ref="A12:N20" headerRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_1" displayName="Tabla_1" ref="A12:N15" headerRowBorderDxfId="6">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PBI / HU"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tarea ID"/>
@@ -1593,7 +1421,7 @@
   <dimension ref="A1:N1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -1609,100 +1437,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="22"/>
+      <c r="A1" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26"/>
     </row>
     <row r="2" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="25"/>
+      <c r="A2" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="4" spans="1:14" ht="15">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="22"/>
+      <c r="B5" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
+      <c r="B6" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
+      <c r="B7" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
@@ -1792,502 +1620,143 @@
     </row>
     <row r="13" spans="1:14" ht="48" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16" t="s">
         <v>6</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
       <c r="N13" s="16" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="48" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="48" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="48" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="s">
-        <v>74</v>
-      </c>
+    <row r="16" spans="1:14" ht="48" customHeight="1"/>
+    <row r="17" spans="1:5" ht="48" customHeight="1"/>
+    <row r="18" spans="1:5" ht="48" customHeight="1"/>
+    <row r="19" spans="1:5" ht="48" customHeight="1">
+      <c r="A19" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="57"/>
     </row>
-    <row r="17" spans="1:14" ht="48" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="48" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="48" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="85.5" customHeight="1">
-      <c r="A20" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="52" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="J20" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="57.95" customHeight="1">
-      <c r="A21" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="H21" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="J21" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="K21" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="57.95" customHeight="1">
-      <c r="A22" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="B22" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="H22" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="K22" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="57" customHeight="1">
-      <c r="A23" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="56"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="56"/>
-    </row>
-    <row r="24" spans="1:14" ht="48.75" customHeight="1">
-      <c r="A24" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="H24" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="I24" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="J24" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="K24" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="48" customHeight="1">
-      <c r="A25" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="H25" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="J25" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="K25" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A26" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1"/>
-    <row r="28" spans="1:14" ht="15.75" customHeight="1"/>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1"/>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1"/>
-    <row r="31" spans="1:14" ht="15.75" customHeight="1"/>
-    <row r="32" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:5" ht="85.5" customHeight="1"/>
+    <row r="21" spans="1:5" ht="57.95" customHeight="1"/>
+    <row r="22" spans="1:5" ht="57.95" customHeight="1"/>
+    <row r="23" spans="1:5" ht="57" customHeight="1"/>
+    <row r="24" spans="1:5" ht="48.75" customHeight="1"/>
+    <row r="25" spans="1:5" ht="48" customHeight="1"/>
+    <row r="26" spans="1:5" ht="38.25" customHeight="1"/>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -3257,19 +2726,18 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
-  <conditionalFormatting sqref="H13:H20">
+  <conditionalFormatting sqref="H13:H15">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H13="Done"</formula>
     </cfRule>
@@ -3287,16 +2755,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="E13:E20" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H13:H15" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"Pendiente,En progreso,Bloqueado,Done"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F13:F15" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="D13:D15" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Backend,Testing"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E13:E15" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Crítica,Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="D13:D19" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Backend,Testing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H13:H20" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"Pendiente,En progreso,Bloqueado,Done"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F13:F20" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3320,44 +2788,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
-      <c r="A1" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
+      <c r="A1" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="26"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="25"/>
+      <c r="A2" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="29"/>
     </row>
     <row r="3" spans="1:16" ht="22.5" customHeight="1"/>
     <row r="4" spans="1:16" ht="22.5" customHeight="1"/>
@@ -3412,7 +2880,7 @@
     <row r="6" spans="1:16" ht="42.75" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="18" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -3449,13 +2917,13 @@
         <v/>
       </c>
       <c r="P6" s="18" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="48.75" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -3484,7 +2952,7 @@
         <v/>
       </c>
       <c r="N7" s="8" t="str">
-        <f t="shared" ref="N6:N13" si="6">IF(C7="","",SUM(D7,F7,H7,J7,L7))</f>
+        <f t="shared" ref="N7:N13" si="6">IF(C7="","",SUM(D7,F7,H7,J7,L7))</f>
         <v/>
       </c>
       <c r="O7" s="8" t="str">
@@ -3492,13 +2960,13 @@
         <v/>
       </c>
       <c r="P7" s="5" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="51" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="5" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -3535,13 +3003,13 @@
         <v/>
       </c>
       <c r="P8" s="5" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="54" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -3578,13 +3046,13 @@
         <v/>
       </c>
       <c r="P9" s="5" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="74.25" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="5" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -3621,13 +3089,13 @@
         <v/>
       </c>
       <c r="P10" s="5" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="60.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="5" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -3664,13 +3132,13 @@
         <v/>
       </c>
       <c r="P11" s="5" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="66" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="5" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -3707,94 +3175,94 @@
         <v/>
       </c>
       <c r="P12" s="5" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="69.75" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57" t="str">
+      <c r="B13" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57" t="str">
+      <c r="F13" s="21"/>
+      <c r="G13" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57" t="str">
+      <c r="H13" s="21"/>
+      <c r="I13" s="21" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57" t="str">
+      <c r="J13" s="21"/>
+      <c r="K13" s="21" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57" t="str">
+      <c r="L13" s="21"/>
+      <c r="M13" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N13" s="58" t="str">
+      <c r="N13" s="22" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O13" s="58" t="str">
+      <c r="O13" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P13" s="57" t="s">
-        <v>140</v>
+      <c r="P13" s="21" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="38.1" customHeight="1">
       <c r="A14" s="14"/>
-      <c r="B14" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55" t="s">
-        <v>141</v>
+      <c r="B14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="38.1" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55" t="s">
-        <v>142</v>
+      <c r="B15" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4808,17 +4276,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25">
-      <c r="A1" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="A1" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="6" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
@@ -4827,33 +4295,33 @@
         <v>3</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="9" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="B4" s="9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" ref="E4:E6" si="0">B6</f>
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="9" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" si="0"/>
@@ -4862,13 +4330,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="9" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="B6" s="9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="0"/>
@@ -4877,35 +4345,35 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="B7" s="9">
         <v>0</v>
       </c>
-      <c r="D7" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="59">
+      <c r="D7" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="9" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B8" s="9">
         <v>0</v>
       </c>
-      <c r="D8" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" s="55">
+      <c r="D8" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="9" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11">
         <v>1</v>
@@ -4913,70 +4381,70 @@
     </row>
     <row r="10" spans="1:5" ht="71.25">
       <c r="A10" s="9" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="71.25">
+    <row r="11" spans="1:5" ht="57">
       <c r="A11" s="9" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="D14" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="22"/>
+      <c r="A14" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="D14" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="46"/>
+      <c r="A15" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="50"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="46"/>
+      <c r="D15" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="50"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="48"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="47"/>
-      <c r="B17" s="48"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="52"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="52"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="47"/>
-      <c r="B18" s="48"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="48"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="52"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="48"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="52"/>
     </row>
     <row r="20" spans="1:5" ht="94.5" customHeight="1">
-      <c r="A20" s="49"/>
-      <c r="B20" s="50"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="54"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
       <c r="A21" s="12"/>
@@ -4985,43 +4453,43 @@
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5" ht="24" customHeight="1">
-      <c r="A22" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="22"/>
+      <c r="A22" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
     <row r="23" spans="1:5" ht="72" customHeight="1">
-      <c r="A23" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
+      <c r="A23" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="36"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="41"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="41"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="44"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="28" spans="1:5" ht="15.75" customHeight="1"/>
